--- a/data/trans_camb/P1804_2016_2023-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1804_2016_2023-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-2,28</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,4</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,31</t>
+          <t>-1,94; 5,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 1,79</t>
+          <t>-6,45; 2,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,61</t>
+          <t>-2,83; 3,06</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-17,24%</t>
+          <t>-15,35%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-4,05%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,84; 80,11</t>
+          <t>-21,86; 103,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-43,44; 17,74</t>
+          <t>-39,78; 24,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 32,38</t>
+          <t>-25,03; 36,51</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,61</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,82</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,42</t>
+          <t>2,67</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 8,07</t>
+          <t>1,08; 8,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 4,95</t>
+          <t>-3,69; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,54</t>
+          <t>-0,11; 5,64</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>35,47%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,34; 241,94</t>
+          <t>10,13; 272,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 65,75</t>
+          <t>-27,85; 70,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 91,55</t>
+          <t>-3,22; 91,38</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-1,77</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-2,94</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,78</t>
+          <t>-1,77; 5,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 3,36</t>
+          <t>-8,85; 4,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 1,16</t>
+          <t>-2,41; 3,8</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-28,07%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-24,65%</t>
+          <t>-21,76%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-29,2%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,41; 32,81</t>
+          <t>-24,17; 109,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-62,81; 47,06</t>
+          <t>-59,36; 52,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-72,5; 16,03</t>
+          <t>-27,69; 59,07</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-1,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-2,06</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; -1,02</t>
+          <t>-4,57; -0,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -0,61</t>
+          <t>-4,19; 1,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,96; -1,22</t>
+          <t>-3,7; -0,41</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-41,73%</t>
+          <t>-37,67%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-36,74%</t>
+          <t>-13,91%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-37,25%</t>
+          <t>-24,8%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-61,04; -16,81</t>
+          <t>-57,1; -8,78</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,28; -6,96</t>
+          <t>-35,44; 13,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,3; -15,88</t>
+          <t>-39,66; -5,2</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-0,75</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,52</t>
+          <t>-3,31; 2,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,19</t>
+          <t>-4,23; 1,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,11</t>
+          <t>-2,76; 1,12</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>-6,31%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-24,73%</t>
+          <t>-13,91%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-13,22%</t>
+          <t>-9,46%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,37; 78,38</t>
+          <t>-47,55; 58,81</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 2,91</t>
+          <t>-37,08; 18,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 16,25</t>
+          <t>-30,51; 16,77</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>-4,19</t>
+          <t>-4,13</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-3,66</t>
+          <t>-3,56</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,87</t>
+          <t>-3,72</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; -0,77</t>
+          <t>-7,32; -0,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,84; -1,33</t>
+          <t>-5,99; -1,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -2,08</t>
+          <t>-5,65; -1,85</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>-73,26%</t>
+          <t>-72,16%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-43,27%</t>
+          <t>-42,13%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-49,12%</t>
+          <t>-47,13%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-95,99; 13,15</t>
+          <t>-95,58; 28,19</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-59,11; -17,97</t>
+          <t>-59,29; -20,06</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-63,61; -29,33</t>
+          <t>-62,06; -25,66</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-1,54</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,64</t>
+          <t>-0,83</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 0,65</t>
+          <t>-1,39; 1,26</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,34; -1,07</t>
+          <t>-2,88; -0,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,63</t>
+          <t>-1,75; 0,13</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-12,2%</t>
+          <t>-1,57%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-25,01%</t>
+          <t>-15,49%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-20,08%</t>
+          <t>-10,16%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,49; 11,45</t>
+          <t>-20,13; 22,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-40,02; -11,42</t>
+          <t>-26,49; -2,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -7,96</t>
+          <t>-20,33; 1,7</t>
         </is>
       </c>
     </row>
